--- a/Relay2026_v8_1_PRODUCTION_ROOT_FILES/Relay2026_Data.xlsx
+++ b/Relay2026_v8_1_PRODUCTION_ROOT_FILES/Relay2026_Data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chiaramanton/Library/Mobile Documents/com~apple~CloudDocs/RAGNAR RELAY/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE09E7DF-7E20-6D42-BDAD-269EF97F2C82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0569EEF3-1072-9248-9E3D-70B15FA830CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20080" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12480" yWindow="660" windowWidth="22080" windowHeight="20060" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Runners" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="827" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="839" uniqueCount="304">
   <si>
     <t>#</t>
   </si>
@@ -929,6 +929,30 @@
   </si>
   <si>
     <t>Parent</t>
+  </si>
+  <si>
+    <t>emily.umulis@gmail.com</t>
+  </si>
+  <si>
+    <t>612-501-0468</t>
+  </si>
+  <si>
+    <t>Mike Huguenel</t>
+  </si>
+  <si>
+    <t>305-497-5684</t>
+  </si>
+  <si>
+    <t>Eduardo Pelaez</t>
+  </si>
+  <si>
+    <t>Brother</t>
+  </si>
+  <si>
+    <t>786-510-0370</t>
+  </si>
+  <si>
+    <t>David Umulis</t>
   </si>
 </sst>
 </file>
@@ -998,7 +1022,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -1012,9 +1036,12 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1328,7 +1355,7 @@
         <v>24</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D5" s="3">
         <v>175.9</v>
@@ -1354,7 +1381,7 @@
         <v>28</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D6" s="3">
         <v>175.9</v>
@@ -1365,7 +1392,7 @@
       <c r="F6" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="G6" s="7"/>
+      <c r="G6" s="5"/>
       <c r="H6" s="2" t="s">
         <v>30</v>
       </c>
@@ -1430,7 +1457,7 @@
         <v>40</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D9" s="3">
         <v>175.9</v>
@@ -1482,7 +1509,7 @@
         <v>49</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D11" s="3">
         <v>175.9</v>
@@ -1534,7 +1561,7 @@
         <v>57</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D13" s="3">
         <v>175.9</v>
@@ -1612,7 +1639,7 @@
         <v>69</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D16" s="3">
         <v>175.9</v>
@@ -1623,8 +1650,12 @@
       <c r="F16" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
+      <c r="G16" s="8" t="s">
+        <v>296</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>297</v>
+      </c>
     </row>
     <row r="17" spans="1:8" ht="15">
       <c r="A17" s="2">
@@ -1634,7 +1665,7 @@
         <v>71</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D17" s="3">
         <v>175.9</v>
@@ -1645,7 +1676,7 @@
       <c r="F17" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="G17" s="7"/>
+      <c r="G17" s="5"/>
       <c r="H17" s="2" t="s">
         <v>73</v>
       </c>
@@ -2014,13 +2045,13 @@
       <c r="B2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="8" t="s">
         <v>89</v>
       </c>
     </row>
@@ -2031,13 +2062,13 @@
       <c r="B3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="8" t="s">
         <v>92</v>
       </c>
     </row>
@@ -2048,13 +2079,13 @@
       <c r="B4" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="8" t="s">
         <v>95</v>
       </c>
     </row>
@@ -2065,13 +2096,13 @@
       <c r="B5" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="8" t="s">
         <v>295</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="8" t="s">
         <v>97</v>
       </c>
     </row>
@@ -2082,13 +2113,13 @@
       <c r="B6" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="8" t="s">
         <v>295</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="8" t="s">
         <v>97</v>
       </c>
     </row>
@@ -2099,13 +2130,13 @@
       <c r="B7" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="8" t="s">
         <v>100</v>
       </c>
     </row>
@@ -2116,13 +2147,13 @@
       <c r="B8" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="8" t="s">
         <v>289</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" s="8" t="s">
         <v>290</v>
       </c>
     </row>
@@ -2133,9 +2164,15 @@
       <c r="B9" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
+      <c r="C9" s="8" t="s">
+        <v>298</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>299</v>
+      </c>
     </row>
     <row r="10" spans="1:5" ht="15">
       <c r="A10" s="2">
@@ -2144,13 +2181,13 @@
       <c r="B10" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E10" s="8" t="s">
         <v>103</v>
       </c>
     </row>
@@ -2161,11 +2198,13 @@
       <c r="B11" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2" t="s">
+      <c r="D11" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="E11" s="8" t="s">
         <v>105</v>
       </c>
     </row>
@@ -2176,13 +2215,13 @@
       <c r="B12" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="E12" s="8" t="s">
         <v>108</v>
       </c>
     </row>
@@ -2193,9 +2232,15 @@
       <c r="B13" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
+      <c r="C13" s="8" t="s">
+        <v>300</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>301</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>302</v>
+      </c>
     </row>
     <row r="14" spans="1:5" ht="15">
       <c r="A14" s="2">
@@ -2204,13 +2249,13 @@
       <c r="B14" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="8" t="s">
         <v>291</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="D14" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="E14" s="8" t="s">
         <v>292</v>
       </c>
     </row>
@@ -2221,13 +2266,13 @@
       <c r="B15" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="8" t="s">
         <v>287</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="D15" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="E15" s="8" t="s">
         <v>288</v>
       </c>
     </row>
@@ -2238,9 +2283,15 @@
       <c r="B16" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
+      <c r="C16" s="8" t="s">
+        <v>303</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>297</v>
+      </c>
     </row>
     <row r="17" spans="1:7" ht="15">
       <c r="A17" s="2">
@@ -2249,13 +2300,13 @@
       <c r="B17" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" s="8" t="s">
         <v>293</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="D17" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="E17" s="2" t="s">
+      <c r="E17" s="8" t="s">
         <v>294</v>
       </c>
     </row>
@@ -4488,17 +4539,18 @@
   <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="2" width="40" customWidth="1"/>
+    <col min="1" max="1" width="82.33203125" customWidth="1"/>
+    <col min="2" max="2" width="40" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="21">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
     </row>
     <row r="3" spans="1:5" ht="16">
       <c r="A3" s="4" t="s">
@@ -4524,19 +4576,19 @@
       </c>
       <c r="B6" s="2"/>
     </row>
-    <row r="7" spans="1:5" ht="30">
+    <row r="7" spans="1:5" ht="15">
       <c r="A7" s="2" t="s">
         <v>282</v>
       </c>
       <c r="B7" s="2"/>
     </row>
-    <row r="8" spans="1:5" ht="30">
+    <row r="8" spans="1:5" ht="15">
       <c r="A8" s="2" t="s">
         <v>283</v>
       </c>
       <c r="B8" s="2"/>
     </row>
-    <row r="9" spans="1:5" ht="30">
+    <row r="9" spans="1:5" ht="15">
       <c r="A9" s="2" t="s">
         <v>284</v>
       </c>
